--- a/excel sheets/_source_workbooks/paper_results_fidelity_privacy/2. Alzhimers__fidelity_privacy_metrics.xlsx
+++ b/excel sheets/_source_workbooks/paper_results_fidelity_privacy/2. Alzhimers__fidelity_privacy_metrics.xlsx
@@ -2629,7 +2629,9 @@
       <c r="H2" t="n">
         <v>18.930353</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>7.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2660,7 +2662,9 @@
       <c r="H3" t="n">
         <v>24.770905</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2691,7 +2695,9 @@
       <c r="H4" t="n">
         <v>10.833991</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>14.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2722,7 +2728,9 @@
       <c r="H5" t="n">
         <v>16.343796</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>14.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8195,7 +8203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8241,26 +8249,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other_GAN</t>
+          <t>SDV</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
     </row>
@@ -8270,82 +8278,198 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.5</v>
+        <v>11.7</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Other_GAN</t>
+          <t>SDV</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diffusion</t>
+          <t>SDV</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TVAE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SDV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GaussianCopula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CTABGAN</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Other_GAN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CTABGAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WGAN_GP</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Other_GAN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>WGAN_GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>62</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diffusion</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>TabDDPM</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C9" t="n">
         <v>20.9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D9" t="n">
         <v>14.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E9" t="n">
         <v>54</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Diffusion</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>TabDDPM</t>
         </is>
